--- a/experiments/results/densenet101/CIFAR-10/DICE/adaptive/std/results.xlsx
+++ b/experiments/results/densenet101/CIFAR-10/DICE/adaptive/std/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -666,6 +666,55 @@
       <c r="O6" s="5" t="inlineStr">
         <is>
           <t>dice_p=85,ash_p=None,react_th=None,scale_th=3.0,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>98.95</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>41.71</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>91.84</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>99.48</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>96.95</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>99.43000000000001</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>97.77</v>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=90,ash_p=None,react_th=None,scale_th=3.0,type=std</t>
         </is>
       </c>
     </row>
